--- a/04-analisis/Analisis de Riesgos - Inventario, Matriz de Riesgos y SoA.xlsx
+++ b/04-analisis/Analisis de Riesgos - Inventario, Matriz de Riesgos y SoA.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
